--- a/invoice_lines.xlsx
+++ b/invoice_lines.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -844,6 +844,357 @@
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU &gt;47294573 ibis Styles Hamburg- Barmbek Hamburg HB2AC</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5/23/26 - 5/29/26</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3.Hotel PMS CL Implement - B87620</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>400416031</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU &gt;47294573 ibis Styles Hamburg- Barmbek Hamburg HB2AC</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5/23/26 - 5/29/26</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3.Hotel PMS CL Implement - B87620</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>400416031</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>400335039</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>400335040</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>400335040</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>400335040</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>400335039</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>400335039</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6/27/26 - 7/3/26</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Reporting - Reporting</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>400335039</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invoice_lines.xlsx
+++ b/invoice_lines.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Lines" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Lines" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/invoice_lines.xlsx
+++ b/invoice_lines.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -912,7 +912,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>400335038</t>
+          <t>4000000039</t>
         </is>
       </c>
       <c r="L20" s="2" t="n"/>
@@ -921,162 +921,6 @@
       </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6/27/26 - 7/3/26</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Reporting - Reporting</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>400335038</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6/27/26 - 7/3/26</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Reporting - Reporting</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>400335038</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>6/27/26 - 7/3/26</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Reporting - Reporting</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>400335038</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>HLGIU_NA_Marriott OPERA Cloud deployment</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>6/27/26 - 7/3/26</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Reporting - Reporting</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4000000039</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
